--- a/per-stock/KLIC/financials.xlsx
+++ b/per-stock/KLIC/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5340046848</v>
+        <v>6377807872</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4891969024</v>
+        <v>5929729536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99.06796</v>
+        <v>117.1827</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.084953</v>
+        <v>28.765516</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.9512215</v>
+        <v>8.302092</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.53565</v>
+        <v>0.49803</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17709250</v>
+        <v>4324000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>102.04</v>
+        <v>121.87</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B47:E47)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D38</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C38</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B38</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1714,13 +2182,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1730,6 +2198,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1740,30 +2209,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1785,12 +2259,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-10079370</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>9270414</v>
+        <v>-8361570</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1799,21 +2274,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.255</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.048053</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.122</v>
+        <v>0.21</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1822,21 +2298,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>46524000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>26538000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>10773000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>3831000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>-26037000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>22027000</v>
+        <v>-34217000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1854,12 +2331,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-47997000</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>75987000</v>
+        <v>-39817000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1877,12 +2355,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-47997000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>75987000</v>
+        <v>-39817000</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1891,21 +2370,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1914,21 +2394,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>3978000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>3959000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>4033000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>3917000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>5011000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>5013000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1937,21 +2418,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>122917000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>100670000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>96348000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>79170000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>121602000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>79040000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1960,21 +2442,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>46524000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>26538000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>10773000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3831000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-74034000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>98014000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1983,21 +2466,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>42546000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>22579000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>6740000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-86000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-79045000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>93001000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2006,21 +2490,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>3943000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>4719000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>5813000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>5976000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>5586000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>6325000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2029,21 +2514,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>37000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>39000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>32000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>36000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>27000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2052,21 +2538,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>3980000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>4759000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>5852000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>6008000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>5622000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>6352000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2075,21 +2562,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>-46601370</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>14925414</v>
+        <v>-53063570</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2098,21 +2586,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2121,21 +2610,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>204055000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>181805000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>176670000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>154507000</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>198656000</v>
-      </c>
       <c r="F17" s="3" t="n">
-        <v>155462000</v>
+        <v>206836000</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2144,21 +2634,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>38566000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>17820000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>888000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-6094000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-84667000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>86649000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2167,21 +2658,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>53121000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>52521000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>52464000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>52692000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>53311000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>54212000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2190,21 +2682,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>52327000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>52319000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>52093000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>52692000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>53311000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>53791000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2213,21 +2706,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-1.59</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1.51</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2236,21 +2730,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-1.59</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>1.52</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2259,21 +2754,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2282,21 +2778,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2305,21 +2802,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2328,21 +2826,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2351,21 +2850,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2374,21 +2874,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>7361000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>5743000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>322000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>3171000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>5438000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>11332000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2397,21 +2898,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>42509000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>22539000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>6701000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-118000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-79081000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>92974000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2420,17 +2922,18 @@
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n">
-        <v>-47997000</v>
-      </c>
+      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n">
+        <v>-39817000</v>
+      </c>
+      <c r="G30" s="3" t="n">
         <v>75987000</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="H30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2450,12 +2953,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-47997000</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>75987000</v>
+        <v>-39817000</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2476,9 +2980,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>75987000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2489,11 +2994,12 @@
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2501,18 +3007,21 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n">
+      <c r="B34" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>39817000</v>
       </c>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2525,11 +3034,12 @@
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n">
         <v>8180000</v>
       </c>
-      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2538,21 +3048,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>3943000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>4719000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>5813000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>5976000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>5586000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>6325000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2561,21 +3072,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>37000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>39000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>32000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>36000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>27000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2584,21 +3096,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>3980000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>4759000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>5852000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>6008000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>5622000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>6352000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2607,21 +3120,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>38566000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>17820000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>888000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-6094000</v>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>-36670000</v>
-      </c>
       <c r="F39" s="3" t="n">
-        <v>10662000</v>
+        <v>-44850000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2630,21 +3144,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>81138000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>81135000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>80322000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>75337000</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>77054000</v>
-      </c>
       <c r="F40" s="3" t="n">
-        <v>76422000</v>
+        <v>85234000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2653,21 +3168,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>38396000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>40376000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>38847000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>35741000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>37220000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>37808000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2676,21 +3192,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>42742000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>40759000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>41475000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>39596000</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>39834000</v>
-      </c>
       <c r="F42" s="3" t="n">
-        <v>38614000</v>
+        <v>48014000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2701,11 +3218,12 @@
       <c r="B43" s="3" t="n"/>
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
         <v>39834000</v>
       </c>
-      <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2716,11 +3234,12 @@
       <c r="B44" s="3" t="n"/>
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
         <v>39834000</v>
       </c>
-      <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2729,21 +3248,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>119704000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>98955000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>81210000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>69243000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>40384000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>87084000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2752,21 +3272,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>122917000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>100670000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>96348000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>79170000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>121602000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>79040000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2775,21 +3296,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>242621000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>199625000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>177558000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>148413000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>161986000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>166124000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2798,28 +3320,29 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>242621000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>199625000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>177558000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>148413000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>161986000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>166124000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4499,7 +5022,1991 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>33035000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>33041000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>33444000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>32332000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>52329000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>52323000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>51920000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>52374000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>53032000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>85364000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>85364000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>85364000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>85364000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>85364000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>39786000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>36982000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>38550000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>36349000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>36277000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>783040000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>750221000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>746369000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>762096000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>788429000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>857546000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>825035000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>821491000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>837526000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>864166000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>748797000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>717337000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>713364000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>741737000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>765170000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>783040000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>750221000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>746369000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>762096000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>788429000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>39786000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>36982000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>38550000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>36349000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>36277000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>857546000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>825035000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>821491000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>837526000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>864166000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>857546000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>825035000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>821491000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>837526000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>864166000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>857546000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>825035000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>821491000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>837526000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>864166000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>857546000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>825035000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>821491000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>837526000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>864166000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-23460000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-24707000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-23850000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-21182000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-23331000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-23460000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-24707000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-23850000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-21182000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-23331000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>976253000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>976177000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>974202000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>957392000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>935633000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1229990000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1205569000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1199500000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1203768000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1217808000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>627269000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>620350000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>620043000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>612332000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>605322000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>627269000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>620350000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>620043000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>612332000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>605322000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>328438000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>289605000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>282851000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>287370000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>281098000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>94918000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>92728000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>94680000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>98906000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>98068000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>9143000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>9213000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>10195000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>13269000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>13122000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>17289000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>16851000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>16580000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>20042000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>20156000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>34892000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>35575000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>35533000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>35812000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>35215000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>34892000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>35575000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>35533000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>35812000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>35215000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>33594000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>31089000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>32372000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>29783000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>29575000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>33594000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>31089000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>32372000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>29783000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>29575000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>233520000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>196877000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>188171000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>188464000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>183030000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>4722000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3695000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>3593000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2798000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>3907000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>50749000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>35253000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>33414000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>28712000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>26687000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>50749000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>35253000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>33414000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>28712000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>26687000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>6192000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>5893000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6178000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>6566000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>6702000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>6192000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>5893000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>6178000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>6566000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>6702000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>6623000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>10582000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>12285000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>10497000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>11292000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>165234000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>141454000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>132701000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>139891000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>134442000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46409000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>38879000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>48494000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46170000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>43353000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>118825000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>102575000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>84207000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>93721000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>91089000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dividends Payable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>10727000</v>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>10751000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>10886000</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>10987000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>22653000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>33683000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>27029000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>30235000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>31807000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>22653000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>33683000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>27029000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>30235000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>31807000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>85445000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>68892000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>57178000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>52735000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>48396000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1185984000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1114640000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1104342000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1124896000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1145264000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>203667000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>200426000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>202807000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>194695000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>197064000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>3291000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3197000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3412000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>6531000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>6802000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>16144000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>16460000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>16109000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>17827000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>18716000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>16144000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>16460000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>16109000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>17827000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>18716000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>17881000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>17660000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>16978000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>6107000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>5484000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>17881000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>17660000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>16978000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>6107000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>5484000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Held To Maturity Securities</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>7881000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>7660000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>6978000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>6107000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>5484000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>74506000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>74814000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>75122000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>75430000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>75737000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>4984000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>5292000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>5908000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>6215000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>69522000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>69522000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>69522000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>69522000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>69522000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>91845000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>88295000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>91186000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>88800000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>90325000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>-161549000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>-157530000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>-154679000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-162165000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>-158570000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>253394000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>245825000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>245865000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>250965000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>248895000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>34139000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>33168000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>33793000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>39409000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>39253000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>6699000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>6243000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>5540000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>7036000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>8712000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>33921000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>30827000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>32193000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>29266000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>30207000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>146577000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>143637000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>142446000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>141988000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>140341000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>29876000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>29768000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>29711000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>31084000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>28200000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>2182000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>2182000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>2182000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>2182000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>2182000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>982317000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>914214000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>901535000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>930201000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>948200000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>32549000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>40800000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>47064000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>41551000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>37092000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>206294000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>176507000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>160225000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>158330000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>155655000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Inventories Adjustments Allowances</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>-64647000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>-66394000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>-70502000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-67795000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>-58586000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>78832000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>72085000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>73045000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>66428000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>61237000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>63241000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>53203000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>45725000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>40840000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>39889000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>128868000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>117613000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>111957000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>118857000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>113115000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>255610000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>215779000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>183538000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>173839000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>173934000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>255610000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>215779000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>183538000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>173839000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>173934000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>-65000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>255610000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>215779000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>183538000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>173888000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>173999000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>487864000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>481128000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>510708000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>556481000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>581519000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>199000000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>295000000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>310000000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>295000000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>337864000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>282128000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>215708000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>246481000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>286519000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>283957000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>227331000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>175138000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>193490000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>264599000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>53907000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>54797000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>40570000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>52991000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>21920000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5847,13 +8354,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5863,6 +8370,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5873,30 +8381,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5909,21 +8422,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6194000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-11609000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>4449000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>5290000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>77923000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>8700000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5932,21 +8446,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-165000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-6712000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-17005000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-21613000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-21259000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-37228000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5955,21 +8470,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-114000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-102000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-103000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-101000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-106000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5978,21 +8494,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-4077000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-2676000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-2957000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-2090000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-1954000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-10202000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6001,21 +8518,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>37000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>39000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>32000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>36000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>27000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6024,19 +8542,20 @@
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
         <v>2249000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>3630000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>16974000</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>886000</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>254000</v>
       </c>
     </row>
@@ -6047,21 +8566,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>337864000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>282128000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>215708000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>246481000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>286519000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>278325000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6070,21 +8590,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>282128000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>215708000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>246481000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>286519000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>278325000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>227147000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6093,21 +8614,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>380000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-84000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-1173000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>2651000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>238000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-1311000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6116,21 +8638,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>55356000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>66504000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-29600000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-42689000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>7956000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>52489000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6139,21 +8662,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-283000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-17888000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-38508000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-32606000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-33506000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-48452000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6162,21 +8686,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-283000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-17888000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-38508000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-32606000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-33506000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-48452000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6185,21 +8710,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-335000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-3000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-4000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-1159000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-324000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6208,21 +8734,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-10727000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-21398000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-10886000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-10987000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-10794000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6231,21 +8758,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-10727000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-21398000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-10886000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-10987000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-10794000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6254,21 +8782,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-165000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-6712000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-17005000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-21613000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-21259000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-37228000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6277,21 +8806,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-165000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-6712000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-17005000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-21613000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-21259000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-37228000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6300,21 +8830,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-114000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-102000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-103000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-101000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-106000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6323,21 +8854,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-114000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-102000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-103000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-101000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-106000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6346,21 +8878,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-114000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-102000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-103000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-101000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-106000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6369,21 +8902,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>45368000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>93325000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1502000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-17463000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-38415000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>82039000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6392,21 +8926,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>45368000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>93325000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>1502000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-17463000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-38415000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>82039000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6415,21 +8950,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>96000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-35000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>90000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6438,21 +8974,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>185000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>135000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>205000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6461,21 +8998,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-95000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-89000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-195000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-150000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-115000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6484,21 +9022,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>371000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-541000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-520000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-1521000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>2241000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6507,7 +9046,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>371000</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -6516,12 +9055,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>-73000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>2608000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6533,18 +9073,19 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>-541000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-520000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-1448000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-367000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6553,21 +9094,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-4003000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-2675000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-2957000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-1943000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-1894000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-10202000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6576,21 +9118,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>74000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>147000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>60000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6599,21 +9142,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-4077000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-2676000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-2957000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-2090000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-1954000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-10202000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6622,21 +9166,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>10271000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-8933000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>7406000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>7380000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>79877000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>18902000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6645,21 +9190,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>10271000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-8933000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>7406000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>7380000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>79877000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>18902000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6668,21 +9214,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-35817000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-37664000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-15054000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-6124000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>81769000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-69149000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6691,21 +9238,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-359000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-916000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-398000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>1284000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>956000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-2047000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6714,21 +9262,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>26256000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>9569000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>6928000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>5534000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>3462000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-5974000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6737,21 +9286,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>26256000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>9569000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>6928000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>5534000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>3462000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-5974000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6760,21 +9310,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>36848000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>2644000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>13610000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>7208000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>19104000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-15798000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6783,21 +9334,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-10592000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>6925000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-6682000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-1674000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-15642000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>9824000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6806,21 +9358,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-10592000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>6925000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-6682000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-1674000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-15642000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>9824000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6829,21 +9382,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>8252000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>6172000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-6962000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-2724000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>5562000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>1860000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6852,21 +9406,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-30070000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-20252000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-4715000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-10092000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>-2240000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>-9050000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6875,21 +9430,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-39896000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-32237000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-9907000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-126000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>74029000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-53938000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6898,21 +9454,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>26000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>4028000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>1740000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>9685000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>32122000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>1321000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6921,21 +9478,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>6991000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>5330000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>7800000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>7092000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>7493000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>6141000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6945,12 +9503,13 @@
       </c>
       <c r="B47" s="3" t="n"/>
       <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n">
         <v>-103000</v>
       </c>
-      <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n">
         <v>299000</v>
       </c>
     </row>
@@ -6965,7 +9524,8 @@
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6976,15 +9536,16 @@
         </is>
       </c>
       <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="3" t="n"/>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n">
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6995,21 +9556,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-367000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-308000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>1427000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>1513000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-205000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>10000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7018,21 +9580,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>-367000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>-308000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>1427000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>1513000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>-205000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>10000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7041,21 +9604,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>3978000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>3959000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>4033000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>3917000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>5011000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>5013000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7064,21 +9628,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>3978000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>3959000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>4033000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>3917000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>5011000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>5013000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7087,7 +9652,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>308000</v>
+        <v>307000</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>308000</v>
@@ -7096,12 +9661,13 @@
         <v>308000</v>
       </c>
       <c r="E54" s="3" t="n">
+        <v>308000</v>
+      </c>
+      <c r="F54" s="3" t="n">
         <v>1171000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>1246000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7110,7 +9676,7 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>308000</v>
+        <v>307000</v>
       </c>
       <c r="C55" s="3" t="n">
         <v>308000</v>
@@ -7119,12 +9685,13 @@
         <v>308000</v>
       </c>
       <c r="E55" s="3" t="n">
+        <v>308000</v>
+      </c>
+      <c r="F55" s="3" t="n">
         <v>1171000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>1246000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7133,21 +9700,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>3671000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>3651000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>3725000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>3609000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>3840000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>3767000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7156,21 +9724,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>814000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>-1074000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>501000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>-5295000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>-1101000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>-6076000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7178,16 +9747,17 @@
           <t>Earnings Losses From Equity Investments</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
         <v>-272000</v>
       </c>
-      <c r="C58" s="3" t="n"/>
       <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7196,13 +9766,16 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>-362000</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>-410000</v>
       </c>
-      <c r="C59" s="3" t="n"/>
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7211,21 +9784,22 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>978000</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>-391000</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>1538000</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>-5305000</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>-1028000</v>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>-2867000</v>
-      </c>
       <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7234,21 +9808,22 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
+        <v>-74000</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>-78000</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>-21000</v>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>-107000</v>
-      </c>
       <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7266,12 +9841,13 @@
         <v>0</v>
       </c>
       <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
         <v>73000</v>
       </c>
-      <c r="F62" s="3" t="n">
-        <v>-3227000</v>
-      </c>
       <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7280,28 +9856,29 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
+        <v>35148000</v>
+      </c>
+      <c r="C63" s="3" t="n">
         <v>16796000</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="D63" s="3" t="n">
         <v>6379000</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="E63" s="3" t="n">
         <v>-3289000</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="F63" s="3" t="n">
         <v>-84519000</v>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>81642000</v>
-      </c>
       <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7329,12 +9906,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>'Net Debt' not found in statements — left blank</t>
         </is>
       </c>
     </row>
